--- a/resources/age_structured_deaths_hun.xlsx
+++ b/resources/age_structured_deaths_hun.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CSURITA\PycharmProjects\PythonProject\counterfactual-analysis-vzv\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A5ADB0-E818-441F-9CCA-313224CA7D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6770D664-7715-454F-962D-61B71F517253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="deaths" sheetId="1" r:id="rId1"/>
@@ -4214,7 +4214,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4252,13 +4252,6 @@
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="103" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="50" fillId="0" borderId="0" xfId="103" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="104">
     <cellStyle name="1. jelölőszín" xfId="29" xr:uid="{47446427-A6FA-4E74-A50C-ED14100509F4}"/>
@@ -4394,6 +4387,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="hu-HU"/>
+              <a:t>2015,</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="hu-HU" baseline="0"/>
+              <a:t> 35+</a:t>
+            </a:r>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4789,7 +4812,482 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="hu-HU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="hu-HU"/>
+              <a:t>2015, 0-34</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="hu-HU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>helper!$B$2:$B$54</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="53"/>
+                <c:pt idx="0">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>17</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A707-414B-8D45-74E078EEA20C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="312154160"/>
+        <c:axId val="223687088"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="312154160"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="223687088"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="223687088"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="312154160"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="hu-HU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -5345,20 +5843,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>35279</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>153812</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>451556</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>76202</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>254353</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>134761</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>63852</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>57151</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5378,6 +6392,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>331611</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>71261</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>49388</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>62794</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Diagram 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3F7A743-FF13-62D1-1C5C-597E473EE6ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -33969,43 +35019,43 @@
       <c r="A574" t="s">
         <v>61</v>
       </c>
-      <c r="B574" s="21">
+      <c r="B574">
         <v>1.7797552836484983E-2</v>
       </c>
-      <c r="C574" s="21">
+      <c r="C574">
         <v>1.7797552836484983E-2</v>
       </c>
-      <c r="D574" s="21">
+      <c r="D574">
         <v>1.7797552836484983E-2</v>
       </c>
-      <c r="E574" s="21">
+      <c r="E574">
         <v>1.7797552836484983E-2</v>
       </c>
-      <c r="F574" s="21">
+      <c r="F574">
         <v>1.7797552836484983E-2</v>
       </c>
-      <c r="G574" s="21">
+      <c r="G574">
         <v>1.7797552836484983E-2</v>
       </c>
-      <c r="H574" s="21">
+      <c r="H574">
         <v>1.7797552836484983E-2</v>
       </c>
-      <c r="I574" s="21">
+      <c r="I574">
         <v>1.7797552836484983E-2</v>
       </c>
-      <c r="J574" s="21">
+      <c r="J574">
         <v>1.7797552836484983E-2</v>
       </c>
-      <c r="K574" s="21">
+      <c r="K574">
         <v>1.7797552836484983E-2</v>
       </c>
-      <c r="L574" s="21">
+      <c r="L574">
         <v>1.7797552836484983E-2</v>
       </c>
-      <c r="M574" s="21">
+      <c r="M574">
         <v>1.7797552836484983E-2</v>
       </c>
-      <c r="N574" s="21">
+      <c r="N574">
         <v>1.8777424723861402E-2</v>
       </c>
     </row>
@@ -34013,43 +35063,43 @@
       <c r="A575" t="s">
         <v>62</v>
       </c>
-      <c r="B575" s="21">
+      <c r="B575">
         <v>9.4549499443826474E-3</v>
       </c>
-      <c r="C575" s="21">
+      <c r="C575">
         <v>9.4549499443826474E-3</v>
       </c>
-      <c r="D575" s="21">
+      <c r="D575">
         <v>9.4549499443826474E-3</v>
       </c>
-      <c r="E575" s="21">
+      <c r="E575">
         <v>9.4549499443826474E-3</v>
       </c>
-      <c r="F575" s="21">
+      <c r="F575">
         <v>9.4549499443826474E-3</v>
       </c>
-      <c r="G575" s="21">
+      <c r="G575">
         <v>9.4549499443826474E-3</v>
       </c>
-      <c r="H575" s="21">
+      <c r="H575">
         <v>9.4549499443826474E-3</v>
       </c>
-      <c r="I575" s="21">
+      <c r="I575">
         <v>9.4549499443826474E-3</v>
       </c>
-      <c r="J575" s="21">
+      <c r="J575">
         <v>9.4549499443826474E-3</v>
       </c>
-      <c r="K575" s="21">
+      <c r="K575">
         <v>9.4549499443826474E-3</v>
       </c>
-      <c r="L575" s="21">
+      <c r="L575">
         <v>9.4549499443826474E-3</v>
       </c>
-      <c r="M575" s="21">
+      <c r="M575">
         <v>9.4549499443826474E-3</v>
       </c>
-      <c r="N575" s="21">
+      <c r="N575">
         <v>1.8928733545165683E-2</v>
       </c>
     </row>
@@ -45453,43 +46503,43 @@
       <c r="A835" t="s">
         <v>322</v>
       </c>
-      <c r="B835" s="21">
+      <c r="B835">
         <v>2.5497512437810944E-2</v>
       </c>
-      <c r="C835" s="21">
+      <c r="C835">
         <v>2.5497512437810944E-2</v>
       </c>
-      <c r="D835" s="21">
+      <c r="D835">
         <v>2.5497512437810944E-2</v>
       </c>
-      <c r="E835" s="21">
+      <c r="E835">
         <v>2.5497512437810944E-2</v>
       </c>
-      <c r="F835" s="21">
+      <c r="F835">
         <v>2.5497512437810944E-2</v>
       </c>
-      <c r="G835" s="21">
+      <c r="G835">
         <v>2.5497512437810944E-2</v>
       </c>
-      <c r="H835" s="21">
+      <c r="H835">
         <v>2.5497512437810944E-2</v>
       </c>
-      <c r="I835" s="21">
+      <c r="I835">
         <v>2.5497512437810944E-2</v>
       </c>
-      <c r="J835" s="21">
+      <c r="J835">
         <v>2.5497512437810944E-2</v>
       </c>
-      <c r="K835" s="21">
+      <c r="K835">
         <v>2.5497512437810944E-2</v>
       </c>
-      <c r="L835" s="21">
+      <c r="L835">
         <v>2.5497512437810944E-2</v>
       </c>
-      <c r="M835" s="21">
+      <c r="M835">
         <v>2.5497512437810944E-2</v>
       </c>
-      <c r="N835" s="21">
+      <c r="N835">
         <v>2.620244584404214E-2</v>
       </c>
     </row>
@@ -45497,43 +46547,43 @@
       <c r="A836" t="s">
         <v>323</v>
       </c>
-      <c r="B836" s="21">
+      <c r="B836">
         <v>2.0522388059701493E-2</v>
       </c>
-      <c r="C836" s="21">
+      <c r="C836">
         <v>2.0522388059701493E-2</v>
       </c>
-      <c r="D836" s="21">
+      <c r="D836">
         <v>2.0522388059701493E-2</v>
       </c>
-      <c r="E836" s="21">
+      <c r="E836">
         <v>2.0522388059701493E-2</v>
       </c>
-      <c r="F836" s="21">
+      <c r="F836">
         <v>2.0522388059701493E-2</v>
       </c>
-      <c r="G836" s="21">
+      <c r="G836">
         <v>2.0522388059701493E-2</v>
       </c>
-      <c r="H836" s="21">
+      <c r="H836">
         <v>2.0522388059701493E-2</v>
       </c>
-      <c r="I836" s="21">
+      <c r="I836">
         <v>2.0522388059701493E-2</v>
       </c>
-      <c r="J836" s="21">
+      <c r="J836">
         <v>2.0522388059701493E-2</v>
       </c>
-      <c r="K836" s="21">
+      <c r="K836">
         <v>2.0522388059701493E-2</v>
       </c>
-      <c r="L836" s="21">
+      <c r="L836">
         <v>2.0522388059701493E-2</v>
       </c>
-      <c r="M836" s="21">
+      <c r="M836">
         <v>2.0522388059701493E-2</v>
       </c>
-      <c r="N836" s="21">
+      <c r="N836">
         <v>2.4373711412997431E-2</v>
       </c>
     </row>
@@ -70894,10 +71944,10 @@
       </c>
     </row>
     <row r="524" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A524" s="22" t="s">
+      <c r="A524" s="15" t="s">
         <v>1059</v>
       </c>
-      <c r="B524" s="23">
+      <c r="B524" s="18">
         <v>29</v>
       </c>
       <c r="C524">
